--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -2316,17 +2316,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>rider_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rider_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>product</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2338,17 +2338,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>DTH_MAIN</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>주계약사망</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2360,17 +2360,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>재해사망특약</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2382,17 +2382,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>HOSP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>입원특약</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2404,17 +2404,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>암진단특약</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2426,17 +2426,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ANN</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>연금특약</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2448,17 +2448,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>MAT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>생존특약</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>mat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2506,7 +2506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2522,7 +2522,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2538,7 +2538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2554,7 +2554,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2570,7 +2570,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2586,7 +2586,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2602,7 +2602,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2618,7 +2618,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2634,7 +2634,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2650,7 +2650,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2666,7 +2666,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2682,7 +2682,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2698,7 +2698,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2714,7 +2714,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2730,7 +2730,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2746,7 +2746,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2762,7 +2762,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2778,7 +2778,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2794,7 +2794,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2810,7 +2810,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2826,7 +2826,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2842,7 +2842,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2858,7 +2858,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2874,7 +2874,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2890,7 +2890,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2906,7 +2906,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2922,7 +2922,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2938,7 +2938,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2954,7 +2954,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2970,7 +2970,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2986,7 +2986,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -3002,7 +3002,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -3018,7 +3018,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -3034,7 +3034,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -3050,7 +3050,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3066,7 +3066,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3082,7 +3082,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -3098,7 +3098,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3114,7 +3114,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3130,7 +3130,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3146,7 +3146,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -3162,7 +3162,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3178,7 +3178,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3194,7 +3194,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3210,7 +3210,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3226,7 +3226,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3242,7 +3242,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3258,7 +3258,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3274,7 +3274,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3290,7 +3290,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3306,7 +3306,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3322,7 +3322,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3338,7 +3338,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3354,7 +3354,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3370,7 +3370,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3386,7 +3386,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3402,7 +3402,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3418,7 +3418,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3434,7 +3434,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3450,7 +3450,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3466,7 +3466,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3482,7 +3482,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3498,7 +3498,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3514,7 +3514,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3530,7 +3530,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3546,7 +3546,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3562,7 +3562,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3578,7 +3578,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3594,7 +3594,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3610,7 +3610,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3626,7 +3626,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3642,7 +3642,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3658,7 +3658,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3674,7 +3674,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3690,7 +3690,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3706,7 +3706,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3722,7 +3722,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3738,7 +3738,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3754,7 +3754,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -3770,7 +3770,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3786,7 +3786,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3802,7 +3802,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3818,7 +3818,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3834,7 +3834,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3850,7 +3850,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3866,7 +3866,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3882,7 +3882,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3898,7 +3898,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3914,7 +3914,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3930,7 +3930,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -3946,7 +3946,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3962,7 +3962,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3978,7 +3978,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3994,7 +3994,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4010,7 +4010,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -4026,7 +4026,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4042,7 +4042,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -4058,7 +4058,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4074,7 +4074,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -4090,7 +4090,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4106,7 +4106,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4122,7 +4122,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4138,7 +4138,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4154,7 +4154,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -4170,7 +4170,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -4186,7 +4186,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -4202,7 +4202,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -4218,7 +4218,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4234,7 +4234,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4250,7 +4250,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4266,7 +4266,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -4282,7 +4282,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -4298,7 +4298,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -4314,7 +4314,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4330,7 +4330,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -4346,7 +4346,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -4362,7 +4362,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -4378,7 +4378,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -4394,7 +4394,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -4410,7 +4410,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -4426,7 +4426,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -4442,7 +4442,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -4458,7 +4458,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -4474,7 +4474,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4490,7 +4490,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -4506,7 +4506,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4522,7 +4522,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -4538,7 +4538,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -4554,7 +4554,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -4570,7 +4570,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -4586,7 +4586,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -4602,7 +4602,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -4618,7 +4618,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -4634,7 +4634,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -4650,7 +4650,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -4666,7 +4666,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -4682,7 +4682,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -4698,7 +4698,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -4714,7 +4714,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -4730,7 +4730,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -4746,7 +4746,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -4762,7 +4762,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -4778,7 +4778,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4794,7 +4794,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -4810,7 +4810,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -4826,7 +4826,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -4842,7 +4842,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -4858,7 +4858,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -4874,7 +4874,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -4890,7 +4890,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -4906,7 +4906,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -4922,7 +4922,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -4938,7 +4938,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -4954,7 +4954,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -4970,7 +4970,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -4986,7 +4986,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -5002,7 +5002,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -5018,7 +5018,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -5034,7 +5034,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -5050,7 +5050,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -5066,7 +5066,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5082,7 +5082,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -5098,7 +5098,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -5114,7 +5114,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -5130,7 +5130,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -5146,7 +5146,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -5162,7 +5162,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -5178,7 +5178,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -5194,7 +5194,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -5210,7 +5210,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -5226,7 +5226,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -5242,7 +5242,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -5258,7 +5258,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -5274,7 +5274,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -5290,7 +5290,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -5306,7 +5306,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -5322,7 +5322,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -5338,7 +5338,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -5354,7 +5354,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -5370,7 +5370,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -5386,7 +5386,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -5402,7 +5402,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -5418,7 +5418,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -5434,7 +5434,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -5450,7 +5450,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -5466,7 +5466,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -5482,7 +5482,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -5498,7 +5498,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -5514,7 +5514,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -5530,7 +5530,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -5546,7 +5546,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -5562,7 +5562,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -5578,7 +5578,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -5594,7 +5594,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -5610,7 +5610,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -5626,7 +5626,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -5642,7 +5642,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -5658,7 +5658,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -5674,7 +5674,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5690,7 +5690,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5706,7 +5706,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5722,7 +5722,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5738,7 +5738,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5754,7 +5754,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5770,7 +5770,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5786,7 +5786,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5802,7 +5802,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5818,7 +5818,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5834,7 +5834,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5850,7 +5850,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5866,7 +5866,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5882,7 +5882,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5898,7 +5898,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5914,7 +5914,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5930,7 +5930,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5946,7 +5946,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5962,7 +5962,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5978,7 +5978,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5994,7 +5994,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -6010,7 +6010,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -6026,7 +6026,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -6042,7 +6042,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -6058,7 +6058,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -6074,7 +6074,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -6090,7 +6090,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -6106,7 +6106,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -6122,7 +6122,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -6138,7 +6138,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -6154,7 +6154,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -6170,7 +6170,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -6186,7 +6186,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6202,7 +6202,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -6218,7 +6218,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -6234,7 +6234,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -6250,7 +6250,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -6266,7 +6266,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -6282,7 +6282,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -6298,7 +6298,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -6314,7 +6314,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -6330,7 +6330,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -6346,7 +6346,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -6362,7 +6362,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -6378,7 +6378,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6394,7 +6394,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6410,7 +6410,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6426,7 +6426,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6442,7 +6442,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6458,7 +6458,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6474,7 +6474,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6490,7 +6490,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6506,7 +6506,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6522,7 +6522,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6538,7 +6538,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6554,7 +6554,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6570,7 +6570,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6586,7 +6586,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6602,7 +6602,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6618,7 +6618,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6634,7 +6634,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6650,7 +6650,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6666,7 +6666,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6682,7 +6682,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6698,7 +6698,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6714,7 +6714,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6730,7 +6730,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6746,7 +6746,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6762,7 +6762,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6778,7 +6778,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6794,7 +6794,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6810,7 +6810,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6826,7 +6826,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6842,7 +6842,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6858,7 +6858,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6874,7 +6874,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6890,7 +6890,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6906,7 +6906,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6922,7 +6922,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6938,7 +6938,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6954,7 +6954,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6970,7 +6970,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6986,7 +6986,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -7002,7 +7002,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -7018,7 +7018,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -7034,7 +7034,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -7050,7 +7050,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -7066,7 +7066,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7082,7 +7082,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7098,7 +7098,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7114,7 +7114,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7130,7 +7130,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7146,7 +7146,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7162,7 +7162,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7178,7 +7178,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7194,7 +7194,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7210,7 +7210,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7226,7 +7226,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7242,7 +7242,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7258,7 +7258,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7274,7 +7274,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7290,7 +7290,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7306,7 +7306,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7322,7 +7322,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7338,7 +7338,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7354,7 +7354,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7370,7 +7370,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7386,7 +7386,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7402,7 +7402,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7418,7 +7418,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7434,7 +7434,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7450,7 +7450,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7466,7 +7466,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7482,7 +7482,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7498,7 +7498,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7514,7 +7514,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7530,7 +7530,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7546,7 +7546,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7562,7 +7562,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7578,7 +7578,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7594,7 +7594,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7610,7 +7610,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7626,7 +7626,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7642,7 +7642,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7658,7 +7658,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7674,7 +7674,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7690,7 +7690,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7706,7 +7706,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7722,7 +7722,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7738,7 +7738,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7754,7 +7754,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7770,7 +7770,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -7786,7 +7786,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -7802,7 +7802,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -7818,7 +7818,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -7834,7 +7834,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -7850,7 +7850,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -7866,7 +7866,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -7882,7 +7882,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -7898,7 +7898,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -7914,7 +7914,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -7930,7 +7930,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -7946,7 +7946,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -7962,7 +7962,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -7978,7 +7978,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -7994,7 +7994,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8010,7 +8010,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8026,7 +8026,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8042,7 +8042,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8058,7 +8058,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8074,7 +8074,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8090,7 +8090,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8106,7 +8106,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8122,7 +8122,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8138,7 +8138,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8154,7 +8154,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8170,7 +8170,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8186,7 +8186,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8202,7 +8202,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8218,7 +8218,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8234,7 +8234,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8250,7 +8250,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8266,7 +8266,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8282,7 +8282,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8298,7 +8298,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8314,7 +8314,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8330,7 +8330,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8346,7 +8346,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8362,7 +8362,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8378,7 +8378,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8394,7 +8394,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8410,7 +8410,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8426,7 +8426,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8442,7 +8442,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8458,7 +8458,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -8474,7 +8474,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -8490,7 +8490,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -8506,7 +8506,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -8522,7 +8522,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -8538,7 +8538,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -8554,7 +8554,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -8570,7 +8570,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -8586,7 +8586,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -8602,7 +8602,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -8618,7 +8618,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -8634,7 +8634,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -8650,7 +8650,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -8666,7 +8666,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -8682,7 +8682,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -8698,7 +8698,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -8714,7 +8714,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -8730,7 +8730,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -8746,7 +8746,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -8762,7 +8762,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -8778,7 +8778,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -8794,7 +8794,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -8810,7 +8810,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -8826,7 +8826,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -8842,7 +8842,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -8858,7 +8858,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -8874,7 +8874,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -8890,7 +8890,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -8906,7 +8906,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -8922,7 +8922,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -8938,7 +8938,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -8954,7 +8954,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -8970,7 +8970,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -8986,7 +8986,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -9002,7 +9002,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -9018,7 +9018,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -9034,7 +9034,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -9050,7 +9050,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -9066,7 +9066,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -9082,7 +9082,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -9098,7 +9098,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -9114,7 +9114,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -9130,7 +9130,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -9146,7 +9146,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -9162,7 +9162,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -9178,7 +9178,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -9194,7 +9194,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -9210,7 +9210,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -9226,7 +9226,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -9242,7 +9242,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -9258,7 +9258,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -9274,7 +9274,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -9290,7 +9290,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -9306,7 +9306,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B427" t="n">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>주계약사망</t>
+          <t>main contract death</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>재해사망특약</t>
+          <t>accidental death rider</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>입원특약</t>
+          <t>hospitalization rider</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>암진단특약</t>
+          <t>cancer diagnosis rider</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>연금특약</t>
+          <t>annuity rider</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>생존특약</t>
+          <t>survival benefit rider</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,11 @@
           <t>morbidity_cv</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>state_model</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -525,6 +530,11 @@
       </c>
       <c r="L2" t="n">
         <v>0.12</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>WAIVER</t>
+        </is>
       </c>
     </row>
     <row r="3">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -540,7 +540,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>term_a</t>
+          <t>TERM_A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="segments" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="riders" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="coverages" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="mortality_tables" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="rider_rate_tables" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="waiver_tables" sheetId="5" state="visible" r:id="rId5"/>
@@ -599,12 +599,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>rider_code</t>
+          <t>coverage_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>rider_name</t>
+          <t>coverage_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -10,7 +10,7 @@
     <sheet name="segments" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="coverages" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="mortality_tables" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="rider_rate_tables" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="incidence_rate_tables" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="waiver_tables" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="lapse_tables" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="maintenance_tables" sheetId="7" state="visible" r:id="rId7"/>

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MAINT_STD</t>
+          <t>MAINTENANCE_STD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DISC_STD</t>
+          <t>DISCOUNT_STD</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFL_STD</t>
+          <t>INFLATION_STD</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -609,7 +609,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>benefit_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dth_main</t>
+          <t>DEATH_MAIN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>death_main</t>
+          <t>DEATH_MAIN</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hosp</t>
+          <t>INPATIENT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>morbidity</t>
+          <t>MORBIDITY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>CANCER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>DIAGNOSIS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>adb</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>DEATH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>ANNUITY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>annuity</t>
+          <t>ANNUITY</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>MATURITY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>maturity</t>
+          <t>MATURITY</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -820,7 +820,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -836,7 +836,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -852,7 +852,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -868,7 +868,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -884,7 +884,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -900,7 +900,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -916,7 +916,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -932,7 +932,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -948,7 +948,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -964,7 +964,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -980,7 +980,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -996,7 +996,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1012,7 +1012,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1028,7 +1028,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1044,7 +1044,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1060,7 +1060,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1076,7 +1076,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1092,7 +1092,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1108,7 +1108,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1124,7 +1124,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1140,7 +1140,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1156,7 +1156,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1172,7 +1172,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1188,7 +1188,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1204,7 +1204,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1220,7 +1220,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1252,7 +1252,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1268,7 +1268,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1284,7 +1284,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1300,7 +1300,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1316,7 +1316,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1332,7 +1332,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1348,7 +1348,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1364,7 +1364,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1380,7 +1380,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1396,7 +1396,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1412,7 +1412,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1428,7 +1428,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1444,7 +1444,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1460,7 +1460,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1476,7 +1476,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1492,7 +1492,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1508,7 +1508,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1524,7 +1524,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1540,7 +1540,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1556,7 +1556,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1572,7 +1572,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1588,7 +1588,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1604,7 +1604,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1620,7 +1620,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1636,7 +1636,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1652,7 +1652,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1668,7 +1668,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1684,7 +1684,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1700,7 +1700,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1716,7 +1716,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1732,7 +1732,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1748,7 +1748,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1764,7 +1764,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1780,7 +1780,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1796,7 +1796,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1812,7 +1812,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1828,7 +1828,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1844,7 +1844,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1860,7 +1860,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1876,7 +1876,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1892,7 +1892,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1908,7 +1908,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1924,7 +1924,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1940,7 +1940,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1956,7 +1956,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1972,7 +1972,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1988,7 +1988,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2004,7 +2004,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2020,7 +2020,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2036,7 +2036,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2052,7 +2052,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2068,7 +2068,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2084,7 +2084,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2100,7 +2100,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MORT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2152,7 +2152,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2168,7 +2168,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2184,7 +2184,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2200,7 +2200,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2216,7 +2216,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2232,7 +2232,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2248,7 +2248,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2264,7 +2264,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2280,7 +2280,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2296,7 +2296,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2312,7 +2312,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2328,7 +2328,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2344,7 +2344,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2360,7 +2360,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2376,7 +2376,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2392,7 +2392,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2408,7 +2408,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2424,7 +2424,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2440,7 +2440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2456,7 +2456,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2472,7 +2472,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2488,7 +2488,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2504,7 +2504,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2520,7 +2520,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2536,7 +2536,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2552,7 +2552,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2568,7 +2568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2584,7 +2584,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2600,7 +2600,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2616,7 +2616,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2632,7 +2632,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2648,7 +2648,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2664,7 +2664,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2680,7 +2680,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2696,7 +2696,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2712,7 +2712,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2728,7 +2728,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2744,7 +2744,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2760,7 +2760,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2776,7 +2776,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2792,7 +2792,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2808,7 +2808,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2824,7 +2824,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2840,7 +2840,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2856,7 +2856,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2872,7 +2872,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2888,7 +2888,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2904,7 +2904,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2920,7 +2920,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2936,7 +2936,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2952,7 +2952,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2968,7 +2968,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2984,7 +2984,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3000,7 +3000,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3016,7 +3016,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3032,7 +3032,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3048,7 +3048,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3064,7 +3064,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3080,7 +3080,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3096,7 +3096,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3112,7 +3112,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3128,7 +3128,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3144,7 +3144,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3160,7 +3160,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3176,7 +3176,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3192,7 +3192,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3208,7 +3208,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3224,7 +3224,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3240,7 +3240,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3256,7 +3256,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3272,7 +3272,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3288,7 +3288,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3304,7 +3304,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3320,7 +3320,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3336,7 +3336,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3352,7 +3352,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3368,7 +3368,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3384,7 +3384,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3400,7 +3400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -3416,7 +3416,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3432,7 +3432,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3448,7 +3448,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HOSP_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -7084,7 +7084,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -7100,7 +7100,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7116,7 +7116,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7132,7 +7132,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7148,7 +7148,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7164,7 +7164,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7180,7 +7180,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7196,7 +7196,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7212,7 +7212,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7228,7 +7228,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -7244,7 +7244,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -7260,7 +7260,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7276,7 +7276,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -7292,7 +7292,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7308,7 +7308,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -7324,7 +7324,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -7340,7 +7340,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7356,7 +7356,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -7372,7 +7372,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -7388,7 +7388,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7404,7 +7404,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -7420,7 +7420,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7436,7 +7436,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -7452,7 +7452,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7468,7 +7468,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -7484,7 +7484,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -7500,7 +7500,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7516,7 +7516,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -7532,7 +7532,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7548,7 +7548,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7564,7 +7564,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -7580,7 +7580,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -7596,7 +7596,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -7612,7 +7612,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -7628,7 +7628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -7644,7 +7644,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7660,7 +7660,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -7676,7 +7676,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -7692,7 +7692,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -7708,7 +7708,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7724,7 +7724,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -7740,7 +7740,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -7756,7 +7756,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7772,7 +7772,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7788,7 +7788,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7804,7 +7804,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7820,7 +7820,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -7836,7 +7836,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7852,7 +7852,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -7868,7 +7868,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7884,7 +7884,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7900,7 +7900,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -7916,7 +7916,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -7932,7 +7932,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -7948,7 +7948,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -7964,7 +7964,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -7980,7 +7980,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -7996,7 +7996,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -8012,7 +8012,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -8028,7 +8028,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -8044,7 +8044,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -8060,7 +8060,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -8076,7 +8076,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -8092,7 +8092,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -8108,7 +8108,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -8124,7 +8124,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -8140,7 +8140,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -8156,7 +8156,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -8172,7 +8172,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -8188,7 +8188,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -8204,7 +8204,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -8220,7 +8220,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -8236,7 +8236,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -8252,7 +8252,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -8268,7 +8268,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -8284,7 +8284,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -8300,7 +8300,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -8316,7 +8316,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -8332,7 +8332,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -8348,7 +8348,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -8364,7 +8364,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -8380,7 +8380,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WVR_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -8978,7 +8978,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAINT_STD</t>
+          <t>MAINTENANCE_STD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -9022,7 +9022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DISC_STD</t>
+          <t>DISCOUNT_STD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -9066,7 +9066,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFL_STD</t>
+          <t>INFLATION_STD</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -13,9 +13,8 @@
     <sheet name="incidence_rate_tables" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="waiver_tables" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="lapse_tables" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="maintenance_tables" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="discount_tables" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="inflation_tables" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="discount_tables" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="inflation_tables" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,47 +446,57 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>maintenance_table</t>
+          <t>waiver_table</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>waiver_table</t>
+          <t>discount_table</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>discount_table</t>
+          <t>inflation_table</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>inflation_table</t>
+          <t>ra_confidence</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>expense_acquisition</t>
+          <t>mortality_cv</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ra_confidence</t>
+          <t>morbidity_cv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>mortality_cv</t>
+          <t>state_model</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>morbidity_cv</t>
+          <t>alpha_pct</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>state_model</t>
+          <t>alpha_flat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>beta_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>gamma_flat</t>
         </is>
       </c>
     </row>
@@ -504,37 +513,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MAINTENANCE_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WAIVER_STD</t>
+          <t>DISCOUNT_STD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DISCOUNT_STD</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>INFLATION_STD</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>WAIVER</t>
+        </is>
       </c>
       <c r="L2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>WAIVER</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>60000</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +569,7 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -573,7 +589,7 @@
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -8966,26 +8982,26 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>rate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAINTENANCE_STD</t>
+          <t>DISCOUNT_STD</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>60000</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -9022,50 +9038,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DISCOUNT_STD</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>table_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
           <t>INFLATION_STD</t>
         </is>
       </c>

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -604,31 +604,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>coverage_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>coverage_code</t>
+          <t>coverage_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>coverage_name</t>
+          <t>benefit_type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>benefit_type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>rate_table</t>
         </is>
@@ -637,20 +632,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>DEATH_MAIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEATH_MAIN</t>
+          <t>main contract death</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>main contract death</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
         <is>
           <t>DEATH_MAIN</t>
         </is>
@@ -659,25 +649,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>INPATIENT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INPATIENT</t>
+          <t>hospitalization rider</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hospitalization rider</t>
+          <t>MORBIDITY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>MORBIDITY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>INPATIENT_STD</t>
         </is>
@@ -686,25 +671,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>CANCER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer diagnosis rider</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cancer diagnosis rider</t>
+          <t>DIAGNOSIS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>DIAGNOSIS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>CANCER_STD</t>
         </is>
@@ -713,25 +693,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>accidental death rider</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>accidental death rider</t>
+          <t>DEATH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>DEATH</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>ADB_STD</t>
         </is>
@@ -740,20 +715,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>ANNUITY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANNUITY</t>
+          <t>annuity rider</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>annuity rider</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
         <is>
           <t>ANNUITY</t>
         </is>
@@ -762,20 +732,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>MATURITY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MATURITY</t>
+          <t>survival benefit rider</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>survival benefit rider</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
         <is>
           <t>MATURITY</t>
         </is>

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,41 +556,141 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>TERM_LIFE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LAPSE_GA</t>
+          <t>LAPSE_FC</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERM_A</t>
+          <t>TERM_LIFE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LAPSE_GA</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HEALTH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>FC</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>80000</v>
+      <c r="M5" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HEALTH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LAPSE_GA</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HEALTH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LAPSE_GA</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WHOLE_LIFE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LAPSE_FC</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WHOLE_LIFE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LAPSE_GA</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>350000</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +720,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>benefit_type</t>
+          <t>benefit_pattern</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -17,6 +17,7 @@
     <sheet name="discount_tables" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="inflation_tables" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="surrender_value_tables" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="expense_tables" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19218,13 +19219,376 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>table_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>expense_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>inflation_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EXP_TE_FC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>per_policy_init</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EXP_TE_FC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>per_policy_monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EXP_TE_GA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>per_policy_init</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EXP_TE_GA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>per_policy_monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EXP_HE_FC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>per_policy_init</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EXP_HE_FC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>per_policy_monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EXP_HE_GA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>per_policy_init</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXP_HE_GA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>per_policy_monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EXP_HE_TM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>per_policy_init</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXP_HE_TM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>per_policy_monthly</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EXP_WH_FC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>per_policy_init</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EXP_WH_FC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>per_policy_monthly</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EXP_WH_GA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>per_policy_init</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EXP_WH_GA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>per_policy_monthly</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19308,6 +19672,11 @@
           <t>surrender_value_table</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>expense_table</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19359,7 +19728,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -19384,7 +19753,12 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>80000</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>EXP_TE_FC</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -19404,7 +19778,12 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>150000</v>
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>EXP_TE_GA</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -19424,7 +19803,12 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>100000</v>
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>EXP_HE_FC</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -19444,7 +19828,12 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>180000</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>EXP_HE_GA</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -19464,7 +19853,12 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>40000</v>
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>EXP_HE_TM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -19484,7 +19878,12 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>200000</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>EXP_WH_FC</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -19504,7 +19903,12 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>350000</v>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>EXP_WH_GA</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -17,6 +17,7 @@
     <sheet name="discount_tables" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="surrender_value_tables" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="expense_tables" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="inflation_tables" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +485,6 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>inflation_rate</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,9 +505,6 @@
       <c r="D2" t="n">
         <v>80000</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,9 +525,6 @@
       <c r="D3" t="n">
         <v>60000</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -555,9 +545,6 @@
       <c r="D4" t="n">
         <v>150000</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,9 +565,6 @@
       <c r="D5" t="n">
         <v>60000</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -601,9 +585,6 @@
       <c r="D6" t="n">
         <v>100000</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -624,9 +605,6 @@
       <c r="D7" t="n">
         <v>60000</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -647,9 +625,6 @@
       <c r="D8" t="n">
         <v>180000</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,9 +645,6 @@
       <c r="D9" t="n">
         <v>60000</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -693,9 +665,6 @@
       <c r="D10" t="n">
         <v>40000</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -716,9 +685,6 @@
       <c r="D11" t="n">
         <v>60000</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,9 +705,6 @@
       <c r="D12" t="n">
         <v>200000</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -762,9 +725,6 @@
       <c r="D13" t="n">
         <v>60000</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -785,9 +745,6 @@
       <c r="D14" t="n">
         <v>350000</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -808,7 +765,48 @@
       <c r="D15" t="n">
         <v>60000</v>
       </c>
-      <c r="E15" t="n">
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>table_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INFL_BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -823,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,30 +857,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>inflation_table</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>ra_confidence</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mortality_cv</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>morbidity_cv</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>state_model</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>surrender_value_table</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expense_table</t>
         </is>
@@ -909,21 +912,26 @@
           <t>DISCOUNT_STD</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>INFL_BASE</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>0.75</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.12</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>WAIVER</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>SURRENDER_STD</t>
         </is>
@@ -945,7 +953,7 @@
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>EXP_TE_FC</t>
         </is>
@@ -967,7 +975,7 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>EXP_TE_GA</t>
         </is>
@@ -989,7 +997,7 @@
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>EXP_HE_FC</t>
         </is>
@@ -1011,7 +1019,7 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>EXP_HE_GA</t>
         </is>
@@ -1033,7 +1041,7 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>EXP_HE_TM</t>
         </is>
@@ -1055,7 +1063,7 @@
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>EXP_WH_FC</t>
         </is>
@@ -1077,7 +1085,7 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>EXP_WH_GA</t>
         </is>

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>per_policy_init</t>
+          <t>alpha_fixed</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -519,7 +519,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>per_policy_monthly</t>
+          <t>gamma_fixed</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>per_policy_init</t>
+          <t>alpha_fixed</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>per_policy_monthly</t>
+          <t>gamma_fixed</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>per_policy_init</t>
+          <t>alpha_fixed</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -599,7 +599,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>per_policy_monthly</t>
+          <t>gamma_fixed</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>per_policy_init</t>
+          <t>alpha_fixed</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -639,7 +639,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>per_policy_monthly</t>
+          <t>gamma_fixed</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>per_policy_init</t>
+          <t>alpha_fixed</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>per_policy_monthly</t>
+          <t>gamma_fixed</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>per_policy_init</t>
+          <t>alpha_fixed</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>per_policy_monthly</t>
+          <t>gamma_fixed</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>per_policy_init</t>
+          <t>alpha_fixed</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -759,7 +759,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>per_policy_monthly</t>
+          <t>gamma_fixed</t>
         </is>
       </c>
       <c r="D15" t="n">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,16 +1113,6 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>coverage_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>benefit_pattern</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>rate_table</t>
         </is>
       </c>
@@ -1130,117 +1120,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEATH_MAIN</t>
+          <t>INPATIENT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>main contract death</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DEATH_MAIN</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INPATIENT</t>
+          <t>CANCER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hospitalization rider</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MORBIDITY</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>INPATIENT_STD</t>
+          <t>CANCER_STD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cancer diagnosis rider</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DIAGNOSIS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CANCER_STD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ADB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>accidental death rider</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DEATH</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>ADB_STD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ANNUITY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>annuity rider</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ANNUITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MATURITY</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>survival benefit rider</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MATURITY</t>
         </is>
       </c>
     </row>

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -827,12 +827,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>product_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>channel_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,34 +1120,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INPATIENT</t>
+          <t>DEATH_GENERAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INPATIENT_STD</t>
+          <t>MORTALITY_STD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>INPATIENT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CANCER_STD</t>
+          <t>INPATIENT_STD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CANCER_STD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>ADB</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>ADB_STD</t>
         </is>

--- a/src/fastcashflow/sample_data/sample_assumptions.xlsx
+++ b/src/fastcashflow/sample_data/sample_assumptions.xlsx
@@ -940,7 +940,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TERM_LIFE</t>
+          <t>TERM_LIFE_A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -962,7 +962,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERM_LIFE</t>
+          <t>TERM_LIFE_A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HEALTH</t>
+          <t>HEALTH_A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HEALTH</t>
+          <t>HEALTH_A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HEALTH</t>
+          <t>HEALTH_A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1050,7 +1050,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WHOLE_LIFE</t>
+          <t>WHOLE_LIFE_A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WHOLE_LIFE</t>
+          <t>WHOLE_LIFE_A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,7 +1120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEATH_GENERAL</t>
+          <t>DEATH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1162,6 +1162,18 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>ADB_STD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D307"/>
+  <dimension ref="A1:D429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7443,6 +7455,1958 @@
       </c>
       <c r="D307" t="n">
         <v>0.000175</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
+      <c r="C308" t="n">
+        <v>20</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0</v>
+      </c>
+      <c r="C309" t="n">
+        <v>21</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
+      <c r="C310" t="n">
+        <v>22</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0</v>
+      </c>
+      <c r="C311" t="n">
+        <v>23</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0</v>
+      </c>
+      <c r="C312" t="n">
+        <v>24</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
+      <c r="C313" t="n">
+        <v>25</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
+      <c r="C314" t="n">
+        <v>26</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0</v>
+      </c>
+      <c r="C315" t="n">
+        <v>27</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0</v>
+      </c>
+      <c r="C316" t="n">
+        <v>28</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0</v>
+      </c>
+      <c r="C317" t="n">
+        <v>29</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0</v>
+      </c>
+      <c r="C318" t="n">
+        <v>30</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>0</v>
+      </c>
+      <c r="C319" t="n">
+        <v>31</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.000309</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>0</v>
+      </c>
+      <c r="C320" t="n">
+        <v>32</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.000318</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0</v>
+      </c>
+      <c r="C321" t="n">
+        <v>33</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.000327</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0</v>
+      </c>
+      <c r="C322" t="n">
+        <v>34</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.000336</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0</v>
+      </c>
+      <c r="C323" t="n">
+        <v>35</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.0003449999999999999</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0</v>
+      </c>
+      <c r="C324" t="n">
+        <v>36</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.0003539999999999999</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0</v>
+      </c>
+      <c r="C325" t="n">
+        <v>37</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.0003629999999999999</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0</v>
+      </c>
+      <c r="C326" t="n">
+        <v>38</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.000372</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0</v>
+      </c>
+      <c r="C327" t="n">
+        <v>39</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.000381</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>0</v>
+      </c>
+      <c r="C328" t="n">
+        <v>40</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.00039</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C329" t="n">
+        <v>41</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.000399</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0</v>
+      </c>
+      <c r="C330" t="n">
+        <v>42</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.0004079999999999999</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0</v>
+      </c>
+      <c r="C331" t="n">
+        <v>43</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.000417</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0</v>
+      </c>
+      <c r="C332" t="n">
+        <v>44</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.0004259999999999999</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>0</v>
+      </c>
+      <c r="C333" t="n">
+        <v>45</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.0004349999999999999</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0</v>
+      </c>
+      <c r="C334" t="n">
+        <v>46</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.000444</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0</v>
+      </c>
+      <c r="C335" t="n">
+        <v>47</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.000453</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C336" t="n">
+        <v>48</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.000462</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0</v>
+      </c>
+      <c r="C337" t="n">
+        <v>49</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.0004709999999999999</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>0</v>
+      </c>
+      <c r="C338" t="n">
+        <v>50</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.00048</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>0</v>
+      </c>
+      <c r="C339" t="n">
+        <v>51</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.000489</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>0</v>
+      </c>
+      <c r="C340" t="n">
+        <v>52</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.000498</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0</v>
+      </c>
+      <c r="C341" t="n">
+        <v>53</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.000507</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0</v>
+      </c>
+      <c r="C342" t="n">
+        <v>54</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.000516</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0</v>
+      </c>
+      <c r="C343" t="n">
+        <v>55</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.000525</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0</v>
+      </c>
+      <c r="C344" t="n">
+        <v>56</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.000534</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>0</v>
+      </c>
+      <c r="C345" t="n">
+        <v>57</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.000543</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0</v>
+      </c>
+      <c r="C346" t="n">
+        <v>58</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.0005519999999999999</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0</v>
+      </c>
+      <c r="C347" t="n">
+        <v>59</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.000561</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0</v>
+      </c>
+      <c r="C348" t="n">
+        <v>60</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.00057</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0</v>
+      </c>
+      <c r="C349" t="n">
+        <v>61</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.000579</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0</v>
+      </c>
+      <c r="C350" t="n">
+        <v>62</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.000588</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0</v>
+      </c>
+      <c r="C351" t="n">
+        <v>63</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.000597</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0</v>
+      </c>
+      <c r="C352" t="n">
+        <v>64</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.000606</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
+      <c r="C353" t="n">
+        <v>65</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.0006149999999999999</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0</v>
+      </c>
+      <c r="C354" t="n">
+        <v>66</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.000624</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
+      <c r="C355" t="n">
+        <v>67</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.0006329999999999999</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
+      <c r="C356" t="n">
+        <v>68</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.0006419999999999999</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0</v>
+      </c>
+      <c r="C357" t="n">
+        <v>69</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.0006509999999999999</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0</v>
+      </c>
+      <c r="C358" t="n">
+        <v>70</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.00066</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0</v>
+      </c>
+      <c r="C359" t="n">
+        <v>71</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.0006689999999999999</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0</v>
+      </c>
+      <c r="C360" t="n">
+        <v>72</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.0006779999999999999</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0</v>
+      </c>
+      <c r="C361" t="n">
+        <v>73</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0.000687</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0</v>
+      </c>
+      <c r="C362" t="n">
+        <v>74</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.0006959999999999999</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0</v>
+      </c>
+      <c r="C363" t="n">
+        <v>75</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0.0007049999999999998</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0</v>
+      </c>
+      <c r="C364" t="n">
+        <v>76</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0.0007139999999999999</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0</v>
+      </c>
+      <c r="C365" t="n">
+        <v>77</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0.000723</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0</v>
+      </c>
+      <c r="C366" t="n">
+        <v>78</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.0007319999999999999</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
+      <c r="C367" t="n">
+        <v>79</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.0007409999999999999</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0</v>
+      </c>
+      <c r="C368" t="n">
+        <v>80</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.0007499999999999999</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1</v>
+      </c>
+      <c r="C369" t="n">
+        <v>20</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>1</v>
+      </c>
+      <c r="C370" t="n">
+        <v>21</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>1</v>
+      </c>
+      <c r="C371" t="n">
+        <v>22</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+      <c r="C372" t="n">
+        <v>23</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>1</v>
+      </c>
+      <c r="C373" t="n">
+        <v>24</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>1</v>
+      </c>
+      <c r="C374" t="n">
+        <v>25</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1</v>
+      </c>
+      <c r="C375" t="n">
+        <v>26</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" t="n">
+        <v>27</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>1</v>
+      </c>
+      <c r="C377" t="n">
+        <v>28</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>1</v>
+      </c>
+      <c r="C378" t="n">
+        <v>29</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>1</v>
+      </c>
+      <c r="C379" t="n">
+        <v>30</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>1</v>
+      </c>
+      <c r="C380" t="n">
+        <v>31</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.000309</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>1</v>
+      </c>
+      <c r="C381" t="n">
+        <v>32</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.000318</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" t="n">
+        <v>33</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.000327</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>1</v>
+      </c>
+      <c r="C383" t="n">
+        <v>34</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.000336</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>1</v>
+      </c>
+      <c r="C384" t="n">
+        <v>35</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.0003449999999999999</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>1</v>
+      </c>
+      <c r="C385" t="n">
+        <v>36</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.0003539999999999999</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>1</v>
+      </c>
+      <c r="C386" t="n">
+        <v>37</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.0003629999999999999</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>1</v>
+      </c>
+      <c r="C387" t="n">
+        <v>38</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.000372</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>1</v>
+      </c>
+      <c r="C388" t="n">
+        <v>39</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.000381</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>1</v>
+      </c>
+      <c r="C389" t="n">
+        <v>40</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.00039</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>1</v>
+      </c>
+      <c r="C390" t="n">
+        <v>41</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.000399</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>1</v>
+      </c>
+      <c r="C391" t="n">
+        <v>42</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.0004079999999999999</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>1</v>
+      </c>
+      <c r="C392" t="n">
+        <v>43</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.000417</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>1</v>
+      </c>
+      <c r="C393" t="n">
+        <v>44</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.0004259999999999999</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>1</v>
+      </c>
+      <c r="C394" t="n">
+        <v>45</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.0004349999999999999</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>1</v>
+      </c>
+      <c r="C395" t="n">
+        <v>46</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.000444</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>1</v>
+      </c>
+      <c r="C396" t="n">
+        <v>47</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.000453</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>1</v>
+      </c>
+      <c r="C397" t="n">
+        <v>48</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.000462</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>1</v>
+      </c>
+      <c r="C398" t="n">
+        <v>49</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.0004709999999999999</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>1</v>
+      </c>
+      <c r="C399" t="n">
+        <v>50</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.00048</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>1</v>
+      </c>
+      <c r="C400" t="n">
+        <v>51</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.000489</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>1</v>
+      </c>
+      <c r="C401" t="n">
+        <v>52</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.000498</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" t="n">
+        <v>53</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.000507</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>1</v>
+      </c>
+      <c r="C403" t="n">
+        <v>54</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.000516</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>1</v>
+      </c>
+      <c r="C404" t="n">
+        <v>55</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.000525</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>1</v>
+      </c>
+      <c r="C405" t="n">
+        <v>56</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0.000534</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>1</v>
+      </c>
+      <c r="C406" t="n">
+        <v>57</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0.000543</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>1</v>
+      </c>
+      <c r="C407" t="n">
+        <v>58</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0.0005519999999999999</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>1</v>
+      </c>
+      <c r="C408" t="n">
+        <v>59</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0.000561</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>1</v>
+      </c>
+      <c r="C409" t="n">
+        <v>60</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0.00057</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>1</v>
+      </c>
+      <c r="C410" t="n">
+        <v>61</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.000579</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>1</v>
+      </c>
+      <c r="C411" t="n">
+        <v>62</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.000588</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>1</v>
+      </c>
+      <c r="C412" t="n">
+        <v>63</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0.000597</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>1</v>
+      </c>
+      <c r="C413" t="n">
+        <v>64</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0.000606</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>1</v>
+      </c>
+      <c r="C414" t="n">
+        <v>65</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0.0006149999999999999</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>1</v>
+      </c>
+      <c r="C415" t="n">
+        <v>66</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0.000624</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>1</v>
+      </c>
+      <c r="C416" t="n">
+        <v>67</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0.0006329999999999999</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>1</v>
+      </c>
+      <c r="C417" t="n">
+        <v>68</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0.0006419999999999999</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>1</v>
+      </c>
+      <c r="C418" t="n">
+        <v>69</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0.0006509999999999999</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>1</v>
+      </c>
+      <c r="C419" t="n">
+        <v>70</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0.00066</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>1</v>
+      </c>
+      <c r="C420" t="n">
+        <v>71</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0.0006689999999999999</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>1</v>
+      </c>
+      <c r="C421" t="n">
+        <v>72</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0.0006779999999999999</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" t="n">
+        <v>73</v>
+      </c>
+      <c r="D422" t="n">
+        <v>0.000687</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>1</v>
+      </c>
+      <c r="C423" t="n">
+        <v>74</v>
+      </c>
+      <c r="D423" t="n">
+        <v>0.0006959999999999999</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>1</v>
+      </c>
+      <c r="C424" t="n">
+        <v>75</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0.0007049999999999998</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>1</v>
+      </c>
+      <c r="C425" t="n">
+        <v>76</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0.0007139999999999999</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>1</v>
+      </c>
+      <c r="C426" t="n">
+        <v>77</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0.000723</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>1</v>
+      </c>
+      <c r="C427" t="n">
+        <v>78</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0.0007319999999999999</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>1</v>
+      </c>
+      <c r="C428" t="n">
+        <v>79</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0.0007409999999999999</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>DISEASE_DEATH_STD</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>1</v>
+      </c>
+      <c r="C429" t="n">
+        <v>80</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0.0007499999999999999</v>
       </c>
     </row>
   </sheetData>
